--- a/docs/test-cases/SPM-66_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-66_Test_Cases.xlsx
@@ -1,37 +1,125 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/janelleip/Documents/GitHub/IS212/docs/test-cases/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\IS212\docs\test-cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E3E2F18-EDD0-504B-B91E-8D9E09D10DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F55B8EF-8590-47EA-A8AE-ED2CC492CA62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="Open Questions" sheetId="2" r:id="rId2"/>
-    <sheet name="TC01" sheetId="3" r:id="rId3"/>
-    <sheet name="TC02" sheetId="4" r:id="rId4"/>
-    <sheet name="TC03" sheetId="5" r:id="rId5"/>
-    <sheet name="TC04" sheetId="6" r:id="rId6"/>
-    <sheet name="TC05" sheetId="7" r:id="rId7"/>
-    <sheet name="TC06" sheetId="8" r:id="rId8"/>
-    <sheet name="TC07" sheetId="9" r:id="rId9"/>
-    <sheet name="TC08" sheetId="10" r:id="rId10"/>
-    <sheet name="TC09" sheetId="11" r:id="rId11"/>
-    <sheet name="TC10" sheetId="12" r:id="rId12"/>
+    <sheet name="TC01" sheetId="3" r:id="rId2"/>
+    <sheet name="TC02" sheetId="4" r:id="rId3"/>
+    <sheet name="TC03" sheetId="5" r:id="rId4"/>
+    <sheet name="TC04" sheetId="6" r:id="rId5"/>
+    <sheet name="TC05" sheetId="7" r:id="rId6"/>
+    <sheet name="TC06" sheetId="8" r:id="rId7"/>
+    <sheet name="TC07" sheetId="9" r:id="rId8"/>
+    <sheet name="TC08" sheetId="10" r:id="rId9"/>
+    <sheet name="TC09" sheetId="11" r:id="rId10"/>
+    <sheet name="TC10" sheetId="12" r:id="rId11"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="159">
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Test Case ID</t>
+  </si>
+  <si>
+    <t>SPM-66-TC10</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>Once an event has started, an outstanding offer ends - the Attendee keeps their position - and no place is offered</t>
+  </si>
+  <si>
+    <t>Pre-conditions</t>
+  </si>
+  <si>
+    <t>Run npm run fixtures:spm66 just before this case. 'SPM66 Started Expo' started on 20 Oct 2026 and runs for 100 days; the script gave Hana Quek (1st) an offer for 3 days, which the start ends the next time anyone opens a page. Ravi Nathan is 2nd. Run npm run fixtures:spm66 again after this case.</t>
+  </si>
+  <si>
+    <t>Test Steps</t>
+  </si>
+  <si>
+    <t>1. Log in as hana.quek@example.com / password123 (Hana Quek, an Attendee)
+2. Click 'Notifications' in the sidebar
+3. Click 'My Registrations' in the sidebar and click the 'SPM66 Started Expo' row
+4. Log out, then log in as daniel.tan@connectsphere.com / password123 (the assigned Event Coordinator)
+5. Click 'All Events' in the sidebar, open 'SPM66 Started Expo' and click the 'Attendees' tab</t>
+  </si>
+  <si>
+    <t>Test Data</t>
+  </si>
+  <si>
+    <t>Event: SPM66 Started Expo (started 20 Oct 2026) | Offer ended: Hana Quek (1st) | Ravi Nathan (2nd)</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Step 2: A notification 'Your offer has ended' says 'Your offer of a place for "SPM66 Started Expo" has ended because the event has started. You're still on the waiting list.'
+Step 3: The card shows the badge 'Waiting list' and 'You're number 1 on the waiting list.' - no 'Accept place'.
+Step 5: Hana Quek's row shows 'Number 1 in the queue' and Ravi Nathan's 'Number 2 in the queue'; nobody's shows a place offered, and there is no 'Offer place' button.</t>
+  </si>
+  <si>
+    <t>Created By</t>
+  </si>
+  <si>
+    <t>Janelle</t>
+  </si>
+  <si>
+    <t>Creation Date</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t>Pass/Fail/Not Executed/Blocked</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Executed by</t>
+  </si>
+  <si>
+    <t>Date of Execution</t>
+  </si>
+  <si>
+    <t>Commit</t>
+  </si>
+  <si>
+    <t>9c8e479</t>
+  </si>
+  <si>
+    <t>Step 2: Hana Quek had 'Your offer has ended': 'Your offer of a place for "SPM66 Started Expo" has ended because the event has started. You're still on the waiting list.'
+Step 3: The card showed 'Waiting list' and 'You're number 1 on the waiting list.', with no 'Accept place'.
+Step 5: On Daniel Tan's Attendees tab Hana Quek's row showed 'Number 1 in the queue' and Ravi Nathan's 'Number 2 in the queue'; nobody's showed a place offered, and there was no 'Offer place' button.</t>
+  </si>
+  <si>
+    <t>TAN JORDAN</t>
+  </si>
   <si>
     <t>Story</t>
   </si>
@@ -42,9 +130,6 @@
     <t>Sheet</t>
   </si>
   <si>
-    <t>Test Case ID</t>
-  </si>
-  <si>
     <t>Title</t>
   </si>
   <si>
@@ -187,12 +272,6 @@
   </si>
   <si>
     <t>TC10</t>
-  </si>
-  <si>
-    <t>SPM-66-TC10</t>
-  </si>
-  <si>
-    <t>Once an event has started, an outstanding offer ends - the Attendee keeps their position - and no place is offered</t>
   </si>
   <si>
     <t>AC10</t>
@@ -304,31 +383,7 @@
 prisma/migrations/20261023120000_add_waiting_list_offers/migration.sql</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>Question / ambiguity for the PO or developer</t>
-  </si>
-  <si>
-    <t>Answer</t>
-  </si>
-  <si>
-    <t>DECIDED 2026-10-23: Wording - 'Join waiting list', 'You're on the waiting list.', 'You're number N on the waiting list.', 'Leave waiting list' ('Leave the waiting list for &lt;title&gt;?' / 'Stay on the list'), 'A place is available for you' / 'Accept it by &lt;date&gt;. If you don't, it goes to the next person on the waiting list.' with 'Accept place' and 'Decline' ('Decline this place?' / 'Decline place' / 'Keep the offer'); My Registrations 'Number N in the queue' / 'Place offered - accept by &lt;date&gt;'; Attendees tab 'Place offered until &lt;date&gt;' and 'Offer place' ('Offer the place to &lt;name&gt;?' / 'Not now'). Notifications 'A place is available' and 'Your offer has ended'.</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>Summary</t>
-  </si>
-  <si>
-    <t>Pre-conditions</t>
-  </si>
-  <si>
     <t>Run npm run fixtures:spm66 just before this case, and again after it (it joins the list). 'SPM66 Harbour Summit' (8 Nov 2027) has 2 places, both taken (Uma Pillay, Tomas Reyes), registration open until 31 Oct 2027, and 2 attendees waiting: Hana Quek (1st) and Ravi Nathan (2nd). Siew Ling Goh holds no registration for it.</t>
-  </si>
-  <si>
-    <t>Test Steps</t>
   </si>
   <si>
     <t>1. Log in as siew.ling.goh@example.com / password123 (Siew Ling Goh, an Attendee)
@@ -338,13 +393,12 @@
 5. Click 'My Registrations' in the sidebar</t>
   </si>
   <si>
-    <t>Test Data</t>
-  </si>
-  <si>
     <t>Attendee: Siew Ling Goh | Event: SPM66 Harbour Summit (2 of 2 places taken, 2 waiting) | Dietary requirements: Vegetarian</t>
   </si>
   <si>
-    <t>Expected Result</t>
+    <t>Step 2: The 'Your registration' card shows 'Dietary requirements' and 'Accessibility requirements', then 'This event is full. You can join the waiting list instead.' and a 'Join waiting list' button. There is no 'Register' button.
+Step 4: 'You're on the waiting list.' appears, and the card now shows the badge 'Waiting list', 'You're number 3 on the waiting list.' and a 'Leave waiting list' button.
+Step 5: 'SPM66 Harbour Summit' is listed with the status 'Waiting list' and 'Number 3 in the queue'.</t>
   </si>
   <si>
     <t>Step 2: The 'Your registration' card says 'This event is full. You can join the waiting list instead.' above 'Dietary requirements', 'Accessibility requirements' and a 'Join waiting list' button. There is no 'Register' button.
@@ -352,31 +406,12 @@
 Step 5: 'SPM66 Harbour Summit' is listed with the status 'Waiting list' and 'Number 3 in the queue'.</t>
   </si>
   <si>
-    <t>Created By</t>
-  </si>
-  <si>
-    <t>Janelle</t>
-  </si>
-  <si>
-    <t>Creation Date</t>
-  </si>
-  <si>
-    <t>Actual Result</t>
-  </si>
-  <si>
-    <t>Pass/Fail/Not Executed/Blocked</t>
-  </si>
-  <si>
-    <t>Remarks</t>
-  </si>
-  <si>
-    <t>Executed by</t>
-  </si>
-  <si>
-    <t>Date of Execution</t>
-  </si>
-  <si>
-    <t>Commit</t>
+    <t>Step 2: The 'Your registration' card showed 'Dietary requirements' and 'Accessibility requirements' (both Optional.), then 'This event is full. You can join the waiting list instead.' and 'Join waiting list'. No 'Register' button.
+Step 4: 'You're on the waiting list.' appeared; the card showed 'Waiting list', 'You're number 3 on the waiting list.' and 'Leave waiting list'.
+Step 5: 'SPM66 Harbour Summit' (8 Nov 2027, 09:00-17:00) was listed with 'Waiting list' and 'Number 3 in the queue'.</t>
+  </si>
+  <si>
+    <t>The expected result for step 2 said the full message is above the two fields; it is below them, just above 'Join waiting list'. Step 2's wording was corrected on 2026-10-28; the behaviour meets AC1.</t>
   </si>
   <si>
     <t>npm run fixtures:spm66 has been run (as for SPM-66-TC01). Uma Pillay is registered for 'SPM66 Harbour Summit'; Hana Quek is 1st on its waiting list. Nothing is changed in this case.</t>
@@ -393,6 +428,13 @@
   <si>
     <t>Step 2: The card shows the badge 'Registered', 'You registered on 1 Oct 2026.' and 'Withdraw' - no 'Join waiting list' and no 'Register'.
 Step 4: The card shows the badge 'Waiting list', 'You're number 1 on the waiting list.' and 'Leave waiting list' - no 'Join waiting list'.</t>
+  </si>
+  <si>
+    <t>Step 2: Uma Pillay's card showed 'Registered', 'You registered on 1 Oct 2026.' and 'Withdraw'; no 'Join waiting list' and no 'Register'.
+Step 4: Hana Quek's card showed 'Waiting list', 'You're number 1 on the waiting list.' and 'Leave waiting list'; no 'Join waiting list'.</t>
+  </si>
+  <si>
+    <t>c</t>
   </si>
   <si>
     <t>Run npm run fixtures:spm66 just before this case, and again after it (Hana leaves the list). On 'SPM66 Harbour Summit', Hana Quek is 1st and Ravi Nathan 2nd on the waiting list.</t>
@@ -418,6 +460,13 @@
 Step 8: 'SPM66 Harbour Summit' now shows 'Number 1 in the queue'.</t>
   </si>
   <si>
+    <t>Step 2: Ravi Nathan's 'SPM66 Harbour Summit' row showed 'Waiting list' and 'Number 2 in the queue'.
+Step 4: Hana Quek's card said 'You're number 1 on the waiting list.'
+Step 5: The dialog 'Leave the waiting list for SPM66 Harbour Summit?' said 'You lose your place in the queue. To wait again, you would join at the back of the list.', with 'Leave waiting list' and 'Stay on the list'.
+Step 6: 'You have left the waiting list.' appeared and the card offered 'Join waiting list' again.
+Step 8: Ravi Nathan's row showed 'Number 1 in the queue'.</t>
+  </si>
+  <si>
     <t>Run npm run fixtures:spm66 just before this case, and again after it (Hana accepts). On 'SPM66 Offer Gala', a place was offered to Hana Quek an hour before the script ran; it can be accepted for 3 days.</t>
   </si>
   <si>
@@ -435,6 +484,21 @@
 Step 3: The card shows 'A place is available for you' and 'Accept it by &lt;the same date and time&gt;. If you don't, it goes to the next person on the waiting list.', with 'Accept place' and 'Decline'.
 Step 4: 'You're registered for this event.' appears, and the card shows the badge 'Registered', 'You registered on &lt;today&gt;.' and 'Withdraw'.
 Step 5: 'SPM66 Offer Gala' shows the status 'Registered', with nothing about the queue.</t>
+  </si>
+  <si>
+    <t>Step 2: 'SPM66 Offer Gala' shows the status 'Waiting list' and 'Place offered - accept by 30 Oct 2026, 21:47'.
+Step 3: The card shows 'A place is available for you' and 'Accept it by 30 Oct 2026, 21:47. If you don't, it goes to the next person on the waiting list.', with 'Accept place' and 'Decline'.
+Step 4: 'You're registered for this event.' appears, and the card shows the badge 'Registered', 'You registered on 27 Oct 2026.' and 'Withdraw'.
+Step 5: 'SPM66 Offer Gala' shows the status 'Registered', with nothing about the queue.</t>
+  </si>
+  <si>
+    <t>Step 4: the card redraws after the event reloads; its Registered state was confirmed by opening the event again.</t>
+  </si>
+  <si>
+    <t>Step 2: 'SPM66 Offer Gala' showed 'Waiting list' and 'Place offered - accept by 31 Oct 2026, 21:46' (the offer was made at 21:46 on 28 Oct).
+Step 3: The card showed 'A place is available for you' and 'Accept it by 31 Oct 2026, 21:46. If you don't, it goes to the next person on the waiting list.', with 'Accept place' and 'Decline'.
+Step 4: 'You're registered for this event.' appeared; the card showed 'Registered', 'You registered on 28 Oct 2026.' and 'Withdraw'.
+Step 5: 'SPM66 Offer Gala' showed 'Registered', with nothing about the queue.</t>
   </si>
   <si>
     <t>Run npm run fixtures:spm66 just before this case, and again after it (Uma withdraws). 'SPM66 Withdrawal Forum' has 2 places, both taken (Uma Pillay, Tomas Reyes), with Hana Quek 1st and Ravi Nathan 2nd waiting.</t>
@@ -459,6 +523,12 @@
 Step 8: Although a place came free, the card says 'This event is full. You can join the waiting list instead.' with 'Join waiting list' - no 'Register' - because the place is under offer to Hana.</t>
   </si>
   <si>
+    <t>Step 3: 'You have withdrawn from SPM66 Withdrawal Forum.' appeared.
+Step 5: Hana Quek had an unread notification 'A place is available': 'A place is available for "SPM66 Withdrawal Forum". Accept it by 31 Oct 2026, 22:47, or it goes to the next person on the waiting list.'
+Step 6: 'SPM66 Withdrawal Forum' showed 'Place offered - accept by 31 Oct 2026, 22:47'.
+Step 8: Siew Ling Goh's card said 'This event is full. You can join the waiting list instead.' with 'Join waiting list' and no 'Register'.</t>
+  </si>
+  <si>
     <t>Run npm run fixtures:spm66 just before this case, and again after it (Hana declines). On 'SPM66 Decline Workshop', a place is under offer to Hana Quek (1st); Ravi Nathan is 2nd.</t>
   </si>
   <si>
@@ -478,6 +548,11 @@
 Step 6: 'SPM66 Decline Workshop' shows 'Place offered - accept by &lt;date and time 3 days from now&gt;'.</t>
   </si>
   <si>
+    <t>Step 3: The dialog 'Decline this place?' said 'The place goes to the next person on the waiting list, and you leave the waiting list.', with 'Decline place' and 'Keep the offer'.
+Step 4: 'You have declined the place.' appeared and the card offered 'Join waiting list' again.
+Step 6: Ravi Nathan's 'SPM66 Decline Workshop' row showed 'Place offered - accept by 31 Oct 2026, 22:47' (3 days from the decline).</t>
+  </si>
+  <si>
     <t>Run npm run fixtures:spm66 just before this case. On 'SPM66 Lapsed Offer Talk', a place was offered to Hana Quek 3 days and an hour before the script ran, so it ended an hour ago without an answer. Ravi Nathan is 2nd. The app ends it the next time anyone opens a page. Run npm run fixtures:spm66 again after this case.</t>
   </si>
   <si>
@@ -498,6 +573,18 @@
 Step 6: 'SPM66 Lapsed Offer Talk' shows the status 'Withdrawn'.</t>
   </si>
   <si>
+    <t>Step 2: 'SPM66 Lapsed Offer Talk' shows 'Place offered - accept by 30 Oct 2026, 22:47'.
+Step 3: A notification 'A place is available' names 'SPM66 Lapsed Offer Talk'.
+Step 5: A notification 'Your offer has ended' says 'Your offer of a place for "SPM66 Lapsed Offer Talk" has ended because it wasn't accepted in time, and you have left the waiting list.'
+Step 6: 'SPM66 Lapsed Offer Talk' shows the status 'Withdrawn'.</t>
+  </si>
+  <si>
+    <t>Step 2: Ravi Nathan's 'SPM66 Lapsed Offer Talk' row showed 'Place offered - accept by 31 Oct 2026, 22:47' (3 days from when the page was opened).
+Step 3: An unread notification 'A place is available' named "SPM66 Lapsed Offer Talk".
+Step 5: Hana Quek had 'Your offer has ended': 'Your offer of a place for "SPM66 Lapsed Offer Talk" has ended because it wasn't accepted in time, and you have left the waiting list.'
+Step 6: 'SPM66 Lapsed Offer Talk' showed 'Withdrawn'.</t>
+  </si>
+  <si>
     <t>Run npm run fixtures:spm66 just before this case, and again after it (the offer moves). 'SPM66 Override Showcase' is Daniel Tan's: a place is under offer to Hana Quek (1st); Ravi Nathan is 2nd and Siew Ling Goh 3rd.</t>
   </si>
   <si>
@@ -518,6 +605,18 @@
 Step 6: A notification 'Your offer has ended' says 'The coordinator has offered the place for "SPM66 Override Showcase" to someone else. You're still on the waiting list, in the same position.'</t>
   </si>
   <si>
+    <t>Step 2: Hana Quek's row shows 'Waiting list' and 'Place offered until 30 Oct 2026, 21:47'; Ravi Nathan's 'Number 2 in the queue'; Siew Ling Goh's 'Number 3 in the queue'. Ravi's and Siew Ling's rows have 'Offer place'; Hana's and Uma Pillay's do not.
+Step 3: A dialog 'Offer the place to Siew Ling Goh?' says 'The place now offered to Hana Quek moves to Siew Ling Goh, who has 3 days to accept it. Hana Quek stays on the waiting list in the same position, and both are notified.'
+Step 4: 'Siew Ling Goh has been offered the place.' appears; Siew Ling Goh's row now shows 'Place offered until 30 Oct 2026, 22:50' and Hana Quek's 'Number 1 in the queue'.
+Step 6: A notification 'Your offer has ended' says 'The coordinator has offered the place for "SPM66 Override Showcase" to someone else. You're still on the waiting list, in the same position.'</t>
+  </si>
+  <si>
+    <t>Step 2: Hana Quek's row showed 'Waiting list' and 'Place offered until 31 Oct 2026, 21:48'; Ravi Nathan's 'Number 2 in the queue'; Siew Ling Goh's 'Number 3 in the queue'. Ravi's and Siew Ling's rows had 'Offer place'; Hana's and Uma Pillay's did not.
+Step 3: The dialog 'Offer the place to Siew Ling Goh?' said 'The place now offered to Hana Quek moves to Siew Ling Goh, who has 3 days to accept it. Hana Quek stays on the waiting list in the same position, and both are notified.'
+Step 4: 'Siew Ling Goh has been offered the place.' appeared; Siew Ling Goh's row showed 'Place offered until 31 Oct 2026, 22:48' and Hana Quek's 'Number 1 in the queue' (now with 'Offer place').
+Step 6: Hana Quek had 'Your offer has ended': 'The coordinator has offered the place for "SPM66 Override Showcase" to someone else. You're still on the waiting list, in the same position.'</t>
+  </si>
+  <si>
     <t>npm run fixtures:spm66 has been run. 'SPM66 Override Showcase' is organised by Rachel Ng and assigned to Daniel Tan, with a place under offer to Hana Quek. Nothing is changed in this case.</t>
   </si>
   <si>
@@ -534,34 +633,8 @@
 Step 4: The page says 'Not authorised' - 'You can only view the registrations for events you are responsible for.' - and lists nobody.</t>
   </si>
   <si>
-    <t>Run npm run fixtures:spm66 just before this case. 'SPM66 Started Expo' started on 20 Oct 2026 and runs for 100 days; the script gave Hana Quek (1st) an offer for 3 days, which the start ends the next time anyone opens a page. Ravi Nathan is 2nd. Run npm run fixtures:spm66 again after this case.</t>
-  </si>
-  <si>
-    <t>1. Log in as hana.quek@example.com / password123 (Hana Quek, an Attendee)
-2. Click 'Notifications' in the sidebar
-3. Click 'My Registrations' in the sidebar and click the 'SPM66 Started Expo' row
-4. Log out, then log in as daniel.tan@connectsphere.com / password123 (the assigned Event Coordinator)
-5. Click 'All Events' in the sidebar, open 'SPM66 Started Expo' and click the 'Attendees' tab</t>
-  </si>
-  <si>
-    <t>Event: SPM66 Started Expo (started 20 Oct 2026) | Offer ended: Hana Quek (1st) | Ravi Nathan (2nd)</t>
-  </si>
-  <si>
-    <t>Step 2: A notification 'Your offer has ended' says 'Your offer of a place for "SPM66 Started Expo" has ended because the event has started. You're still on the waiting list.'
-Step 3: The card shows the badge 'Waiting list' and 'You're number 1 on the waiting list.' - no 'Accept place'.
-Step 5: Hana Quek's row shows 'Number 1 in the queue' and Ravi Nathan's 'Number 2 in the queue'; nobody's shows a place offered, and there is no 'Offer place' button.</t>
-  </si>
-  <si>
-    <t>9c8e479</t>
-  </si>
-  <si>
-    <t>Pass</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>c</t>
+    <t>Step 2: As Rachel Ng the Attendees tab listed the waiting list with positions and Hana Quek's 'Place offered until 31 Oct 2026, 21:48', with no 'Offer place' button on any row.
+Step 4: As Priya Raj the page said 'Not authorised' - 'You can only view the registrations for events you are responsible for.' - and listed nobody.</t>
   </si>
 </sst>
 </file>
@@ -723,7 +796,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -749,6 +822,11 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -757,10 +835,8 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -978,7 +1054,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -991,468 +1067,468 @@
     <col min="9" max="9" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="18"/>
+    </row>
+    <row r="3" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="15"/>
-    </row>
-    <row r="3" spans="1:9" ht="14" x14ac:dyDescent="0.15">
-      <c r="A3" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>3</v>
-      </c>
       <c r="C3" s="7" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="42" x14ac:dyDescent="0.15">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
     </row>
-    <row r="5" spans="1:9" ht="28" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
     </row>
-    <row r="6" spans="1:9" ht="42" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
     </row>
-    <row r="7" spans="1:9" ht="28" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
     </row>
-    <row r="8" spans="1:9" ht="42" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
     </row>
-    <row r="9" spans="1:9" ht="28" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
     </row>
-    <row r="10" spans="1:9" ht="42" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C10" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="F10" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>16</v>
-      </c>
       <c r="G10" s="9" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
     </row>
-    <row r="11" spans="1:9" ht="42" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="9" t="s">
         <v>43</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>17</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="1:9" ht="28" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>22</v>
-      </c>
       <c r="F12" s="9" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
     </row>
-    <row r="13" spans="1:9" ht="28" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
     </row>
-    <row r="16" spans="1:9" ht="14" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="17"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" s="18"/>
+    </row>
+    <row r="17" spans="1:9" ht="44.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="17"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="18"/>
+    </row>
+    <row r="18" spans="1:9" ht="31.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="17"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F18" s="18"/>
+    </row>
+    <row r="19" spans="1:9" ht="44.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" s="17"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="F19" s="18"/>
+    </row>
+    <row r="20" spans="1:9" ht="31.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" s="17"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20" s="18"/>
+    </row>
+    <row r="21" spans="1:9" ht="44.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" s="17"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F21" s="18"/>
+    </row>
+    <row r="22" spans="1:9" ht="31.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="17"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="F22" s="18"/>
+    </row>
+    <row r="23" spans="1:9" ht="44.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C23" s="17"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="F23" s="18"/>
+    </row>
+    <row r="24" spans="1:9" ht="31.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" s="17"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F16" s="15"/>
-    </row>
-    <row r="17" spans="1:9" ht="44.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" s="14"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="15"/>
-    </row>
-    <row r="18" spans="1:9" ht="31" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="14"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" s="15"/>
-    </row>
-    <row r="19" spans="1:9" ht="44.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="F19" s="15"/>
-    </row>
-    <row r="20" spans="1:9" ht="31" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" s="14"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F20" s="15"/>
-    </row>
-    <row r="21" spans="1:9" ht="44.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="C21" s="14"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="F21" s="15"/>
-    </row>
-    <row r="22" spans="1:9" ht="31" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F22" s="15"/>
-    </row>
-    <row r="23" spans="1:9" ht="44.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F23" s="15"/>
-    </row>
-    <row r="24" spans="1:9" ht="31" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="9" t="s">
+      <c r="F24" s="18"/>
+    </row>
+    <row r="25" spans="1:9" ht="31.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B24" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" s="14"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" s="15"/>
-    </row>
-    <row r="25" spans="1:9" ht="31" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="17"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="F25" s="18"/>
+    </row>
+    <row r="26" spans="1:9" ht="31.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="14"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="F25" s="15"/>
-    </row>
-    <row r="26" spans="1:9" ht="31" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="F26" s="15"/>
-    </row>
-    <row r="28" spans="1:9" ht="220" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B26" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26" s="17"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="F26" s="18"/>
+    </row>
+    <row r="28" spans="1:9" ht="220.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15"/>
+        <v>105</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -1498,145 +1574,197 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.83203125" customWidth="1"/>
-    <col min="2" max="2" width="56.83203125" customWidth="1"/>
+    <col min="1" max="1" width="24.796875" customWidth="1"/>
+    <col min="2" max="2" width="56.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="31.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="44.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="10" t="s">
-        <v>88</v>
-      </c>
       <c r="B3" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.15">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="58.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="125.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="139.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.15">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="31.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="220" customHeight="1" x14ac:dyDescent="0.15">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="71.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="B9" s="12">
         <v>46322</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" ht="12.75" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
     </row>
-    <row r="12" spans="1:3" ht="196" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" ht="56" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="15">
+        <v>46322</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="5"/>
+    </row>
+    <row r="20" spans="1:2" ht="98.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="15">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Step 2: Hana Quek's row shows 'Waiting list' and 'Place offered until 30 Oct 2026, 21:47'; Ravi Nathan's 'Number 2 in the queue'; Siew Ling Goh's 'Number 3 in the queue'. Ravi's and Siew Ling's rows have 'Offer place'; Hana's and Uma Pillay's do not.
-Step 3: A dialog 'Offer the place to Siew Ling Goh?' says 'The place now offered to Hana Quek moves to Siew Ling Goh, who has 3 days to accept it. Hana Quek stays on the waiting list in the same position, and both are notified.'
-Step 4: 'Siew Ling Goh has been offered the place.' appears; Siew Ling Goh's row now shows 'Place offered until 30 Oct 2026, 22:50' and Hana Quek's 'Number 1 in the queue'.
-Step 6: A notification 'Your offer has ended' says 'The coordinator has offered the place for "SPM66 Override Showcase" to someone else. You're still on the waiting list, in the same position.'</t>
+          <t>86ae9d5</t>
         </is>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="13" x14ac:dyDescent="0.15">
-      <c r="A13" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="13" x14ac:dyDescent="0.15">
-      <c r="A14" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="13" x14ac:dyDescent="0.15">
-      <c r="A15" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="13" x14ac:dyDescent="0.15">
-      <c r="A16" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B16" s="19">
-        <v>46322</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="A17" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -1645,282 +1773,197 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="24.83203125" customWidth="1"/>
-    <col min="2" max="2" width="56.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B1" s="2"/>
-    </row>
-    <row r="2" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="139" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="71.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="13" x14ac:dyDescent="0.15">
-      <c r="A9" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="B9" s="12">
-        <v>46322</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="13" x14ac:dyDescent="0.15">
-      <c r="A11" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="6"/>
-    </row>
-    <row r="12" spans="1:3" ht="56" x14ac:dyDescent="0.15">
-      <c r="A12" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="13" x14ac:dyDescent="0.15">
-      <c r="A13" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="13" x14ac:dyDescent="0.15">
-      <c r="A14" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="13" x14ac:dyDescent="0.15">
-      <c r="A15" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="13" x14ac:dyDescent="0.15">
-      <c r="A16" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B16" s="19">
-        <v>46322</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="A17" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>142</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.83203125" customWidth="1"/>
-    <col min="2" max="2" width="56.83203125" customWidth="1"/>
+    <col min="1" max="1" width="24.796875" customWidth="1"/>
+    <col min="2" max="2" width="56.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="31.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="10" t="s">
-        <v>88</v>
-      </c>
       <c r="B3" s="11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="71.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="71.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="125.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="125.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="31.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="112" customHeight="1" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="112.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="B9" s="12">
         <v>46322</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" ht="12.75" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
     </row>
-    <row r="12" spans="1:3" ht="112" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" ht="112.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>17</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>19</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>21</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B16" s="19">
+        <v>22</v>
+      </c>
+      <c r="B16" s="15">
         <v>46322</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="13" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>142</v>
+        <v>23</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="5"/>
+    </row>
+    <row r="20" spans="1:2" ht="139.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="15">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>86ae9d5</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1929,175 +1972,396 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="75" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="1" max="1" width="24.796875" customWidth="1"/>
+    <col min="2" max="2" width="56.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14" x14ac:dyDescent="0.15">
-      <c r="A1" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="139" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="9">
+    <row r="1" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+    </row>
+    <row r="2" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" s="9"/>
+      <c r="B2" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="44.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="85.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="98.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="44.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="125.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="12">
+        <v>46322</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="12.75" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="6"/>
+    </row>
+    <row r="12" spans="1:3" ht="126" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="12">
+        <v>46322</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="5"/>
+    </row>
+    <row r="20" spans="1:2" ht="152.55000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="58.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="12">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>86ae9d5</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.83203125" customWidth="1"/>
-    <col min="2" max="2" width="56.83203125" customWidth="1"/>
+    <col min="1" max="1" width="24.796875" customWidth="1"/>
+    <col min="2" max="2" width="56.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="31.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="44.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="10" t="s">
-        <v>88</v>
-      </c>
       <c r="B3" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="58.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="112.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="31.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="85.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="10" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="98.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="44.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="125.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="10" t="s">
-        <v>97</v>
-      </c>
       <c r="B8" s="11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="B9" s="12">
         <v>46322</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" ht="12.75" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
     </row>
-    <row r="12" spans="1:3" ht="126" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" ht="56" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="B16" s="12">
         <v>46322</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="13" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>105</v>
+        <v>23</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>142</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="5"/>
+    </row>
+    <row r="20" spans="1:2" ht="85.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="12">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>86ae9d5</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2106,140 +2370,197 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.83203125" customWidth="1"/>
-    <col min="2" max="2" width="56.83203125" customWidth="1"/>
+    <col min="1" max="1" width="24.796875" customWidth="1"/>
+    <col min="2" max="2" width="56.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="31.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="10" t="s">
-        <v>88</v>
-      </c>
       <c r="B3" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.15">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="44.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="112" customHeight="1" x14ac:dyDescent="0.15">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="166.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.15">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="31.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.15">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="152.55000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="B9" s="12">
         <v>46322</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" ht="12.75" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
     </row>
-    <row r="12" spans="1:3" ht="56" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" ht="126" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="B16" s="12">
         <v>46322</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="13" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>105</v>
+        <v>23</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>142</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="5"/>
+    </row>
+    <row r="20" spans="1:2" ht="166.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="12">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>86ae9d5</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2248,140 +2569,197 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.83203125" customWidth="1"/>
-    <col min="2" max="2" width="56.83203125" customWidth="1"/>
+    <col min="1" max="1" width="24.796875" customWidth="1"/>
+    <col min="2" max="2" width="56.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="31.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="10" t="s">
-        <v>88</v>
-      </c>
       <c r="B3" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="44.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="58.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="166" customHeight="1" x14ac:dyDescent="0.15">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="85.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.15">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="31.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="152.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="166.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="B9" s="12">
         <v>46322</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" ht="12.75" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
     </row>
-    <row r="12" spans="1:3" ht="126" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" ht="126" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>19</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="B16" s="12">
         <v>46322</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="13" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>105</v>
+        <v>23</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>142</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="5"/>
+    </row>
+    <row r="20" spans="1:2" ht="166.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="12">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>86ae9d5</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2390,147 +2768,197 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.83203125" customWidth="1"/>
-    <col min="2" max="2" width="56.83203125" customWidth="1"/>
+    <col min="1" max="1" width="24.796875" customWidth="1"/>
+    <col min="2" max="2" width="56.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="44.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="10" t="s">
-        <v>88</v>
-      </c>
       <c r="B3" s="11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="58.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.15">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="179.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.15">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="31.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="166" customHeight="1" x14ac:dyDescent="0.15">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="166.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="B9" s="12">
         <v>46322</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" ht="12.75" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
     </row>
-    <row r="12" spans="1:3" ht="126" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" ht="126" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>Step 2: 'SPM66 Offer Gala' shows the status 'Waiting list' and 'Place offered - accept by 30 Oct 2026, 21:47'.
-Step 3: The card shows 'A place is available for you' and 'Accept it by 30 Oct 2026, 21:47. If you don't, it goes to the next person on the waiting list.', with 'Accept place' and 'Decline'.
-Step 4: 'You're registered for this event.' appears, and the card shows the badge 'Registered', 'You registered on 27 Oct 2026.' and 'Withdraw'.
-Step 5: 'SPM66 Offer Gala' shows the status 'Registered', with nothing about the queue.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>16</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Step 4: the card redraws after the event reloads; its Registered state was confirmed by opening the event again.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>19</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="B16" s="12">
         <v>46322</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="13" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>105</v>
+        <v>23</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>142</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="5"/>
+    </row>
+    <row r="20" spans="1:2" ht="152.55000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="12">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>86ae9d5</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2539,140 +2967,197 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.83203125" customWidth="1"/>
-    <col min="2" max="2" width="56.83203125" customWidth="1"/>
+    <col min="1" max="1" width="24.796875" customWidth="1"/>
+    <col min="2" max="2" width="56.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="31.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="44.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="10" t="s">
-        <v>88</v>
-      </c>
       <c r="B3" s="11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.15">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="44.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="179.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="125.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.15">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="31.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="166" customHeight="1" x14ac:dyDescent="0.15">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="98.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="B9" s="12">
         <v>46322</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" ht="12.75" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
     </row>
-    <row r="12" spans="1:3" ht="126" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" ht="98" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="B16" s="12">
         <v>46322</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="13" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>105</v>
+        <v>23</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>142</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="5"/>
+    </row>
+    <row r="20" spans="1:2" ht="125.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="12">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>86ae9d5</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2681,140 +3166,197 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.83203125" customWidth="1"/>
-    <col min="2" max="2" width="56.83203125" customWidth="1"/>
+    <col min="1" max="1" width="24.796875" customWidth="1"/>
+    <col min="2" max="2" width="56.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="44.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="10" t="s">
-        <v>88</v>
-      </c>
       <c r="B3" s="11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="44.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="85.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="125.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="112.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.15">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="31.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="98.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="139.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="B9" s="12">
         <v>46322</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" ht="12.75" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
     </row>
-    <row r="12" spans="1:3" ht="98" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" ht="112.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="B16" s="12">
         <v>46322</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="13" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>105</v>
+        <v>23</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>142</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="5"/>
+    </row>
+    <row r="20" spans="1:2" ht="139.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="12">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>86ae9d5</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2823,145 +3365,197 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.83203125" customWidth="1"/>
-    <col min="2" max="2" width="56.83203125" customWidth="1"/>
+    <col min="1" max="1" width="24.796875" customWidth="1"/>
+    <col min="2" max="2" width="56.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="44.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="44.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="10" t="s">
-        <v>88</v>
-      </c>
       <c r="B3" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.15">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="58.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="112" customHeight="1" x14ac:dyDescent="0.15">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="125.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.15">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="31.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="139" customHeight="1" x14ac:dyDescent="0.15">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="220.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="B9" s="12">
         <v>46322</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" ht="12.75" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
     </row>
-    <row r="12" spans="1:3" ht="112" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" ht="196.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="15">
+        <v>46322</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="5"/>
+    </row>
+    <row r="20" spans="1:2" ht="247.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="17.55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="15">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="13.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Step 2: 'SPM66 Lapsed Offer Talk' shows 'Place offered - accept by 30 Oct 2026, 22:47'.
-Step 3: A notification 'A place is available' names 'SPM66 Lapsed Offer Talk'.
-Step 5: A notification 'Your offer has ended' says 'Your offer of a place for "SPM66 Lapsed Offer Talk" has ended because it wasn't accepted in time, and you have left the waiting list.'
-Step 6: 'SPM66 Lapsed Offer Talk' shows the status 'Withdrawn'.</t>
+          <t>86ae9d5</t>
         </is>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="13" x14ac:dyDescent="0.15">
-      <c r="A13" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="13" x14ac:dyDescent="0.15">
-      <c r="A14" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="13" x14ac:dyDescent="0.15">
-      <c r="A15" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="13" x14ac:dyDescent="0.15">
-      <c r="A16" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B16" s="12">
-        <v>46322</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="A17" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>142</v>
       </c>
     </row>
   </sheetData>
